--- a/光伏配储项目/电价数据/2026/鹅村站.xlsx
+++ b/光伏配储项目/电价数据/2026/鹅村站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51069</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.77988</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.58521</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6113099999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5200199999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5139</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43752</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44115</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4233</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40884</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41301</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.23991</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12807</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10396</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11823</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10657</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13049</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07606</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.14641</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.19431</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.14135</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.01837</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09123000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.11866</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04169</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17666</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.22663</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18012</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23941</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.08323999999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.13412</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.19919</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20789</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.7018</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.50702</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.56721</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.31602</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.65163</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.49719</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4721</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57986</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47646</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.63739</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8248099999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64764</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.64698</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7971699999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.14893</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.44377</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.69009</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58777</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.81472</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6087899999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.60462</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65301</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.62487</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47857</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4779</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42561</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70821</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.55462</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7603</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.35341</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.80776</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5287200000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5187999999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50519</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51081</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48919</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40252</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59745</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.70226</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.42583</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43231</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.52278</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.21581</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37893</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06681999999999999</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.4631</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.46367</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.4679700000000001</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.42947</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.46611</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.52046</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.74237</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.27398</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39457</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5800700000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.99405</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5234800000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.14258</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.47211</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.51646</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.49677</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.44217</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29686</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.43521</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.6243500000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7585</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.61764</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70414</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.76705</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.73975</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.6345</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.5692699999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.75867</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.57733</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.5337000000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.00127</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.46146</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.5648</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6766</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.46722</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.47473</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.43016</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33455</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51336</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.8228</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.69278</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42153</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.54626</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.46041</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.47985</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47381</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.47884</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.47299</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.41712</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.05128</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.72758</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.7636799999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.21852</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.21412</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26798</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.4799</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5270499999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49221</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.42959</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17047</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28611</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.42993</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.52385</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40231</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5643400000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6397200000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7140700000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.47592</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.4975</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.42586</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.47836</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45212</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47301</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45905</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34241</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.41734</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45905</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22924</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.24876</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.46457</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.47244</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56867</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.46562</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.57966</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.46894</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.14232</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.09712</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.26803</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.43139</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.25323</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.7408400000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07251000000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.1913</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.26065</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.26638</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23243</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24794</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21843</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.13142</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.43037</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.61514</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4685299999999999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.44926</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29973</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.40618</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27906</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26009</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.11084</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.0438</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.10877</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.12149</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04458</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04562</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.07823000000000001</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04647999999999999</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.0345</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04852</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.0425</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.0425</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04261</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04216</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04259</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04542</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04191</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.0417</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04314</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04568999999999999</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21849</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04502</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05109</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05592</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.03749</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01789</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.04301</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.21943</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.12269</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41688</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35084</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.74866</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44609</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04372</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04381</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04408</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10304</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00203</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04356</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04313</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04324</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04329</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04516</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04406</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04388</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04448</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04725</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04763000000000001</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14299</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33564</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3179</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28824</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27119</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17256</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15881</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17112</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14786</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15959</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15876</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23641</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21418</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22673</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27186</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29605</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45462</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15636</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909400000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78107</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92052</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91608</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86787</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29933</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89288</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63266</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19241</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8714500000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5450499999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33624</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03666</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53613</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7954600000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53026</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77749</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78111</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8773300000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87621</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49735</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40533</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21243</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87905</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55115</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62725</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5396799999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4992799999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43814</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43377</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58647</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42769</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5959800000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60236</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66826</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47351</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58166</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45243</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88202</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63463</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.93864</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.92079</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86507</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6155499999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41002</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41263</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45233</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35343</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92422</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46691</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47723</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49995</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16576</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26256</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19912</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19862</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43516</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59654</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8903799999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.37184</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.17208</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7114400000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8061499999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6611399999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58953</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45501</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50688</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.44169</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41855</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42728</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50684</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43823</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41598</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43896</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.43191</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45503</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42727</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5041</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.51595</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.87491</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.48726</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.53123</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25254</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.85903</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.08721</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.46789</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.45155</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.5934700000000001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26433</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41173</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5794199999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46671</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7868099999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.47015</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43723</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42167</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32394</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.50558</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.48137</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.45805</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23495</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24197</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.24619</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.17496</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.22796</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.17494</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.22468</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.21973</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.41853</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.21537</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.18404</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.20555</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.22675</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.23326</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.4506</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.44122</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.4685299999999999</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.6169600000000001</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40317</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45247</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4465</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44247</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44685</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44721</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34875</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54539</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41883</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38174</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.2004</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24873</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24151</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26852</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.25146</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27466</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24057</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28402</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.22924</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.17022</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.25759</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.18746</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.24785</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42045</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36111</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.40871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.50896</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43211</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44219</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44948</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.05552</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25006</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.17796</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.23126</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25987</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.46116</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7060700000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5187999999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26194</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28682</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34953</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42408</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64398</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.79337</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.44518</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46089</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3416</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26436</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.1417</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28477</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20075</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26166</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28082</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.2234</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28076</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43853</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.69325</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5926900000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.45398</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.68237</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.77846</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43252</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46739</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47771</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41414</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35997</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52628</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47746</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48504</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3953</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40901</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41047</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41114</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4215</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45414</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44804</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5641699999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50593</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45442</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.24725</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44584</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47606</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43037</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46275</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46621</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6502100000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.17191</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44257</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49823</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4424</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.51866</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5037</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.45632</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.61886</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.70539</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.70336</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81048</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5840700000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.51428</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.79988</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.74224</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6245000000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6619700000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44374</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47449</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47731</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46102</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55161</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42983</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44156</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45142</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42181</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44213</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41011</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44981</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21228</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40462</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46347</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11737</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18072</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.45461</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43004</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39501</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36529</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44485</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22734</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23072</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25057</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26582</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13977</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25387</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18336</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28518</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22905</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24993</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26713</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23252</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35001</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26468</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25087</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17168</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21314</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24682</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.0009699999999999999</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02599</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11844</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01258</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03904</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01071</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03632</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03254</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04717</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04654999999999999</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02311</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.15328</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04909</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04889</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00113</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03135</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04907</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04881</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04193</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18504</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20404</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.24168</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26894</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27483</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28633</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.16004</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.6133</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.40975</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.18785</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.26002</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27787</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26419</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23543</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26329</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25482</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.2830299999999999</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26118</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28614</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.18461</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.67218</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.66586</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.68203</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.6227200000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.18315</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.1193</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24631</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.19813</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.14074</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.14711</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.10613</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23334</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.06966</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.11977</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.18694</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02324</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.14018</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.14915</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.16376</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.00886</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.12281</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.13381</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.13261</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16744</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25885</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.44926</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3234</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.56068</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5353</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42481</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.43469</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.45542</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44624</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14179</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27021</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46422</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32737</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.57564</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.54828</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49686</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26314</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41421</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40566</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48331</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.49203</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.58494</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.45967</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.5755800000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.41816</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41629</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36453</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48117</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.43867</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.44306</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.41352</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.46469</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27498</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.49369</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.46189</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43497</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50385</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57041</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.57133</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.44721</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.52923</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49859</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5363600000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.52062</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.47774</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.5628500000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7851699999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55589</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55938</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.43308</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36966</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26418</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24224</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17099</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17748</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07137</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20816</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.03856</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21696</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17434</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.00733</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26463</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16924</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06344</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05611</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07607</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17409</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08386</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06085</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18181</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17804</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42495</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38885</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42246</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36315</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8489099999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47202</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43272</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.27054</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26377</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11652</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01246</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.00958</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03885</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.16412</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03278</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00542</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01885</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04609000000000001</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01789</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01146</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16316</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04555</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24823</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.17303</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.26976</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.49016</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.54814</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.27297</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36396</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.57972</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.2388</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14882</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21553</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23939</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24334</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1189</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15749</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02353</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.02663</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04719</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04721</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04574</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04628</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04459</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08112999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02862</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06442000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09988</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20576</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12557</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27062</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05906</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26922</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.15406</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.12142</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2435</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19434</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.25032</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.25557</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21229</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28613</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40088</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46067</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37316</v>
       </c>
     </row>
   </sheetData>
